--- a/Company_Input_v2.xlsx
+++ b/Company_Input_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shubhamhorambe/Documents/Company_Builder_App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E62C43D-B2BB-B743-AE4E-D9EAD3D45BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BA60CE-1F44-804C-A9D1-0FF46F1F2813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" tabRatio="924" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
